--- a/brand-protection/2026-09-28/strike/02-mono_mixed.xlsx
+++ b/brand-protection/2026-09-28/strike/02-mono_mixed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>Tags</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +461,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +478,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,6 +495,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,6 +512,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +529,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -511,6 +546,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +563,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -535,6 +580,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -547,6 +597,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -559,6 +614,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -571,6 +631,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -583,6 +648,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -595,6 +665,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -607,6 +682,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -619,6 +699,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -631,6 +716,11 @@
           <t>strike-02-mono-mixed</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -641,6 +731,11 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
         </is>
       </c>
     </row>

--- a/brand-protection/2026-09-28/strike/02-mono_mixed.xlsx
+++ b/brand-protection/2026-09-28/strike/02-mono_mixed.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sample" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,23 +413,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>url</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>website_category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>email_address</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>wechat</t>
         </is>
       </c>
     </row>
@@ -441,12 +491,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bartlettcabinet.com</t>
         </is>
       </c>
     </row>
@@ -458,12 +518,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>churchonhigherground.org</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>echoslonska.com</t>
         </is>
       </c>
     </row>
@@ -492,12 +567,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ethicalpublicdomain.org</t>
         </is>
       </c>
     </row>
@@ -509,12 +589,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mmostbetcasinos-uz.net</t>
         </is>
       </c>
     </row>
@@ -526,12 +611,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mostbesttop.com</t>
         </is>
       </c>
     </row>
@@ -543,12 +638,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mostbet-27.net</t>
         </is>
       </c>
     </row>
@@ -560,12 +660,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mostbetaz.kz</t>
         </is>
       </c>
     </row>
@@ -577,12 +687,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mostbetaz.online</t>
         </is>
       </c>
     </row>
@@ -594,12 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mostbetcasino-uz.com</t>
         </is>
       </c>
     </row>
@@ -611,12 +736,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>myparuchia.com</t>
         </is>
       </c>
     </row>
@@ -628,12 +758,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>penniesfortheplanet.org</t>
         </is>
       </c>
     </row>
@@ -645,12 +780,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>progressiveislam.info</t>
         </is>
       </c>
     </row>
@@ -662,12 +802,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sleater-kinney.org</t>
         </is>
       </c>
     </row>
@@ -679,12 +824,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>st-martory.com</t>
         </is>
       </c>
     </row>
@@ -696,12 +851,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>una-unso.info</t>
         </is>
       </c>
     </row>
@@ -713,12 +873,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>unbridledspeculation.com</t>
         </is>
       </c>
     </row>
@@ -730,12 +900,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>strike-02-mono-mixed</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-02-mono-mixed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yoxvalleypartnership.org</t>
         </is>
       </c>
     </row>
